--- a/Configs/GameConfig/Datas/fg/#GridTerrain-地形类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#GridTerrain-地形类型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>pattern</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>navCost</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +534,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>叠加层图案:none/hatch/dots/waves/cross/grid</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>地面单位通行代价倍率(FG0-ARCH-06 层级寻路):0=不可通行,1=正常,2~15=绕着走更划算;不影响移动速度</t>
         </is>
       </c>
     </row>
@@ -555,6 +570,9 @@
           <t>none</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -584,6 +602,9 @@
           <t>waves</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -613,6 +634,9 @@
           <t>dots</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -642,6 +666,9 @@
           <t>dots</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -671,6 +698,9 @@
           <t>grid</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -700,6 +730,9 @@
           <t>grid</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -728,6 +761,9 @@
         <is>
           <t>hatch</t>
         </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
